--- a/Tables/Data/__beans__.xlsx
+++ b/Tables/Data/__beans__.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -732,6 +732,40 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>描述（可空）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>EItemCategory</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>类别（Material/Consumable/Clue/Key）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>
